--- a/hypotheses/tables/alphas-state-graph.xlsx
+++ b/hypotheses/tables/alphas-state-graph.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,70 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Partnership-frame outperforms cheat-code positioning для L2 outreach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>recognized</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-002-partnership-frame-better-than-cheatcode-l2.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H-003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3-tier funnel (Tier-1 entry workshop → Tier-2 cohort → Tier-3 partner) 3-6 month lifecycle optimal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>recognized</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-003-3tier-funnel-3to6-months-optimal.md</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -482,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -525,6 +589,70 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Partnership-frame outperforms cheat-code positioning для L2 outreach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-002-partnership-frame-better-than-cheatcode-l2.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H-003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3-tier funnel (Tier-1 entry workshop → Tier-2 cohort → Tier-3 partner) 3-6 month lifecycle optimal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>solution_needed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-003-3tier-funnel-3to6-months-optimal.md</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -536,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -579,6 +707,70 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3-tier funnel (Tier-1 entry workshop → Tier-2 cohort → Tier-3 partner) 3-6 month lifecycle optimal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bounded</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-003-3tier-funnel-3to6-months-optimal.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H-004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Imagination as 13th component of intellect-stack (extension к Левенчук 12-component model)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>conceived</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-004-imagination-as-intellect-component.md</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -590,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -633,6 +825,38 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-005</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Method as 1st-class object enables recursive self-improvement engine (per Левенчук MG4 + Jetix substrate)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>demonstrable</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-005-method-as-1st-class-object-recursive-engine.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -644,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -684,6 +908,70 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Last updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta-method (cycle + discipline + output + reflection) applicable cross-domain beyond engineering</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>prepared</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-001-meta-method-success-formula-applicable-cross-domain.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H-005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Method as 1st-class object enables recursive self-improvement engine (per Левенчук MG4 + Jetix substrate)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>under_control</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-005-method-as-1st-class-object-recursive-engine.md</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -752,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -795,6 +1083,102 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta-method (cycle + discipline + output + reflection) applicable cross-domain beyond engineering</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>foundation_established</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-001-meta-method-success-formula-applicable-cross-domain.md</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H-004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Imagination as 13th component of intellect-stack (extension к Левенчук 12-component model)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>principles_established</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-004-imagination-as-intellect-component.md</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H-005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Method as 1st-class object enables recursive self-improvement engine (per Левенчук MG4 + Jetix substrate)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>foundation_established</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-005-method-as-1st-class-object-recursive-engine.md</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
